--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0029.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0029.xlsx
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Một cánh cổng mở ra. Cao nguyên Desorock. Somnoire xuất hiện. Một tập hợp những giấc mơ...</t>
+          <t>Một cánh cổng mở ra. Desorock Highland. Somnoire xuất hiện. Một tập hợp những giấc mơ...</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Meow!</t>
+          <t>Meo!</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Làm tốt lắm, meo meo. Ta biết là có thể trông cậy vào ngươi!</t>
+          <t>Làm tốt lắm, meo meo. Tao biết là có thể trông cậy vào mày!</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Không đâu, ta chỉ thích trồng chúng thôi.</t>
+          <t>Không đâu, tao chỉ thích trồng chúng thôi.</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Ta nghe nói cậu đã giúp Shorekeeper và cả bọn thoát khỏi một mớ hỗn độn lớn phải không?</t>
+          <t>Tao nghe nói cậu đã giúp Shorekeeper và cả bọn thoát khỏi một mớ hỗn độn lớn phải không?</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>"Ồ, chúc mừng nhé, {Male=anh;Female=chị} Nổi Tiếng!" Dù gì thì cũng...</t>
+          <t>"Ồ, chúc mừng nhé, {Male=Mr.;Female=Ms.} Nổi Tiếng!" Dù gì thì cũng...</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Haha! Chắc ta chẳng còn lựa chọn nào khác nhỉ?</t>
+          <t>Haha! Chắc tao chẳng còn lựa chọn nào khác nhỉ?</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Cậu không thấy giống nhau sao? Nói ta nghe, cậu đã nghĩ gì khi chứng kiến những câu chuyện đó, khi dán mắt vào từng khung hình trên màn hình?</t>
+          <t>Cậu không thấy giống nhau sao? Nói tao nghe, cậu đã nghĩ gì khi chứng kiến những câu chuyện đó, khi dán mắt vào từng khung hình trên màn hình?</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Dù sao thì ta vẫn tin vào trực giác của mình hơn là những ký ức xa xôi kia.</t>
+          <t>Dù sao thì tao vẫn tin vào trực giác của mình hơn là những ký ức xa xôi kia.</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Ôi, thế thì thi thố nhé—ta tham gia! Bắt đầu tìm kiếm thôi!</t>
+          <t>Ôi, thế thì thi thố nhé—tao tham gia! Bắt đầu tìm kiếm thôi!</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>{Male=Anh ấy;Female=Cô ấy} chậm quá đi. Ehe, có vẻ như em thắng rồi.</t>
+          <t>{Male=He's;Female=She's} chậm quá đi. Ehe, có vẻ như em thắng rồi.</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Ôi, cậu thật là dễ thương quá. Em đỏ mặt đến nơi rồi này.</t>
+          <t>Ôi, bạn thật là dễ thương quá. Em đỏ mặt đến nơi rồi này.</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>À phải rồi. Giờ ta mới nhớ cái cảm giác kỳ lạ lúc nãy là gì.</t>
+          <t>À phải rồi. Giờ tao mới nhớ cái cảm giác kỳ lạ lúc nãy là gì.</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Khi gặp lại cậu ở Kim Châu... Cảm giác như ta đã từng gặp cậu ở đâu đó rồi.</t>
+          <t>Khi gặp lại cậu ở Jinzhou... Cảm giác như ta đã từng gặp cậu ở đâu đó rồi.</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>{PlayerName} năn nỉ ta đi cùng {Male=anh ấy;Female=cô ấy}, mà trông có vẻ vui nên ta đồng ý.</t>
+          <t>{PlayerName} năn nỉ ta đi cùng {Male=him;Female=her}, mà trông có vẻ vui nên ta đồng ý.</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Thật sao?</t>
+          <t>Thật chứ?</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Dù sao thì tôi cũng là {Male=anh hùng;Female=nữ anh hùng} mà!</t>
+          <t>Dù sao thì tôi cũng là {Male=hero;Female=heroine} mà!</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Không, ta thấy thế này ổn rồi. Không cần phải mạo hiểm mở cái gì đó rồi lại nằm trong cái buồng y tế nữa.</t>
+          <t>Không, tao thấy thế này ổn rồi. Không cần phải mạo hiểm mở cái gì đó rồi lại nằm trong cái buồng y tế nữa.</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Đứng mãi với quá khứ làm gì. Ta thích sống cho hiện tại hơn.</t>
+          <t>Đứng mãi với quá khứ làm gì. Tao thích sống cho hiện tại hơn.</t>
         </is>
       </c>
     </row>
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -17149,7 +17149,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Sẽ có nhiều khu vực mô phỏng khác nhau. Để đến đích, cậu cần &lt;color=Highlight&gt;find and jump to the correct timeline junctures&lt;/color&gt;.</t>
+          <t>Sẽ có nhiều khu vực mô phỏng khác nhau. Để đến đích, cậu cần &lt;color=Highlight&gt;tìm và nhảy vào đúng các điểm giao thời gian&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Có thể cần &lt;color=Highlight&gt;Multiple jumps&lt;/color&gt; mới tới được đó. {PlayerName}, hãy cẩn thận nhé!</t>
+          <t>Có thể cần &lt;color=Highlight&gt;nhảy nhiều lần&lt;/color&gt; mới tới được đó. {PlayerName}, hãy cẩn thận nhé!</t>
         </is>
       </c>
     </row>
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Thưa Chủ nhân, Cộng Hưởng Giả "Quý Cô Flora" đã vượt ngưỡng giới hạn và rời khỏi buồng y tế rồi.</t>
+          <t>Thưa Chủ nhân, Resonator "Quý Cô Flora" đã vượt ngưỡng giới hạn và rời khỏi buồng y tế rồi.</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Ta đưa cậu về buồng y tế ngay.</t>
+          <t>Tao đưa cậu về buồng y tế ngay.</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Đầu ta... cả người ta... đau hết cả...</t>
+          <t>Đầu tao... cả người tao... đau hết cả...</t>
         </is>
       </c>
     </row>
@@ -19099,7 +19099,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Xin chào, chắc hẳn cậu là {PlayerName} phải không? Beatrice đã kể cho tôi nghe về chuyện xảy ra rồi.</t>
+          <t>Xin chào, chắc hẳn bạn là {PlayerName} phải không? Beatrice đã kể cho tôi nghe về chuyện xảy ra rồi.</t>
         </is>
       </c>
     </row>
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>{Male=Hắn;Female=Cô ta} luôn bị bao phủ trong bí ẩn, và chỉ một số ít người từng gặp {Male=hắn;Female=cô ta}.</t>
+          <t>{Male=him;Female=her} luôn bị bao phủ trong bí ẩn, và chỉ một số ít người từng gặp {Male=him;Female=her}.</t>
         </is>
       </c>
     </row>
@@ -22349,7 +22349,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22804,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Ngươi cần học cách kỷ luật đi, đồ máy móc. Dám cắt ngang cuộc trò chuyện của ta với {Male=hắn;Female=cô ta} à?</t>
+          <t>Mày cần học cách kỷ luật đi, đồ máy móc. Dám cắt ngang cuộc trò chuyện của tao với {Male=him;Female=her} à?</t>
         </is>
       </c>
     </row>
@@ -23064,7 +23064,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>(Bản ghi của KU-Riri có nhắc đến &lt;color=Highlight&gt;Camellya was found in an underground cave&lt;/color&gt;. Có vẻ lần này ta đã nhảy đúng thời điểm rồi.)</t>
+          <t>(Bản ghi của KU-Riri có nhắc đến &lt;color=Highlight&gt;Camellya được tìm thấy trong một hang động ngầm&lt;/color&gt;. Có vẻ lần này tao đã nhảy đúng thời điểm rồi.)</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Hay là... cậu chọn ta làm Người Mang Sắc Hoa của cậu đi? Cậu thấy đấy... còn ai khác có thể ngăn ta gây rắc rối ở nơi khác chứ?</t>
+          <t>Hay là... cậu chọn tao làm Người Mang Sắc Hoa của cậu đi? Cậu thấy đấy... còn ai khác có thể ngăn tao gây rắc rối ở nơi khác chứ?</t>
         </is>
       </c>
     </row>
@@ -25924,7 +25924,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Ảnh rất tuyệt để lưu giữ kỷ niệm. Chụp vài tấm ảnh ta đi.</t>
+          <t>Ảnh rất tuyệt để lưu giữ kỷ niệm. Chụp vài tấm ảnh tao đi.</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26379,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Đẹp đấy. Ta cũng muốn giữ lại một bản này.</t>
+          <t>Đẹp đấy. Tao cũng muốn giữ lại một bản này.</t>
         </is>
       </c>
     </row>
@@ -27354,7 +27354,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>{PlayerName}, nếu muốn dùng món đồ chơi đó để tìm ma trận trục trặc, thì chơi với ta đi! Làm ta vui, ta sẽ giúp cậu.</t>
+          <t>{PlayerName}, nếu muốn dùng món đồ chơi đó để tìm ma trận trục trặc, thì chơi với tao đi! Làm tao vui, tao sẽ giúp cậu.</t>
         </is>
       </c>
     </row>
@@ -27484,7 +27484,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Nếu tôi nói không thì sao?</t>
+          <t>Nếu tớ từ chối thì sao?</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Cậu có thể thử bắt ta, nhưng đừng mong dễ dàng đâu nhé. Hoặc là cậu chịu chơi theo, biết đâu ta sẽ cho cậu cái đó. Cũng vui đấy chứ!</t>
+          <t>Cậu có thể thử bắt tao, nhưng đừng mong dễ dàng đâu nhé. Hoặc là cậu chịu chơi theo, biết đâu tao sẽ cho cậu cái đó. Cũng vui đấy chứ!</t>
         </is>
       </c>
     </row>
@@ -28004,7 +28004,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>...Ta sẽ cực kỳ, cực kỳ, cực kỳ không vui đấy.</t>
+          <t>...Tao sẽ cực kỳ, cực kỳ, cực kỳ không vui đấy.</t>
         </is>
       </c>
     </row>
@@ -28329,7 +28329,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Ta muốn gì, ta sẽ lấy được. Đó là cách ta sống.</t>
+          <t>Tao muốn gì, tao sẽ lấy được. Đó là cách tao sống.</t>
         </is>
       </c>
     </row>
@@ -28654,7 +28654,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Nói chuyện phiếm đủ rồi. Ta sẽ chơi.</t>
+          <t>Nói chuyện phiếm đủ rồi. Tao sẽ chơi.</t>
         </is>
       </c>
     </row>
@@ -28849,7 +28849,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Chuyện gì đang xảy ra vậy?</t>
+          <t>Có chuyện gì vậy?</t>
         </is>
       </c>
     </row>
@@ -29499,7 +29499,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Có gì đó dưới đất à? Ta phải đi xem thử.</t>
+          <t>Có gì đó dưới đất à? Tao phải đi xem thử.</t>
         </is>
       </c>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Trước khi vượt qua bài đánh giá, ta đã đi hỏi mấy người Làm Vườn về vài điều quan trọng mà chúng ta nên biết.</t>
+          <t>Trước khi vượt qua bài đánh giá, tao đã đi hỏi mấy người Làm Vườn về vài điều quan trọng mà chúng ta nên biết.</t>
         </is>
       </c>
     </row>
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Không, ta còn việc khác phải giải quyết trước đã.</t>
+          <t>Không, tao còn việc khác phải giải quyết trước đã.</t>
         </is>
       </c>
     </row>
@@ -31124,7 +31124,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Nhưng {PlayerName} đã đưa ra lựa chọn của {Male=mình;Female=mình} rồi. Giờ đến lượt ta phải đưa ra lựa chọn của riêng mình.</t>
+          <t>Nhưng {PlayerName} đã đưa ra lựa chọn của {Male=his;Female=her} rồi. Giờ đến lượt ta phải đưa ra lựa chọn của riêng mình.</t>
         </is>
       </c>
     </row>
@@ -32099,7 +32099,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Có gì đó không ổn. Ta sẽ đưa ngươi ra khỏi Ma Trận Stellar trước!</t>
+          <t>Có gì đó không ổn. Tao sẽ đưa mày ra khỏi Ma Trận Stellar trước!</t>
         </is>
       </c>
     </row>
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Thật tiếc khi tớ bị lạc mất {Male=anh ấy;Female=chị ấy}.</t>
+          <t>Thật tiếc khi tớ bị lạc mất {Male=him;Female=her}.</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Ước gì {Male=cậu ấy;Female=cô ấy} có thể thấy những gì tôi vừa thấy trong những dòng thời gian khác. Không thể chờ để xem phản ứng của {Male=cậu ấy;Female=cô ấy} đâu.</t>
+          <t>Ước gì {Male=his;Female=her} có thể thấy những gì tôi vừa thấy trong những dòng thời gian khác. Không thể chờ để xem phản ứng của {Male=his;Female=her} đâu.</t>
         </is>
       </c>
     </row>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Nhưng {PlayerName} đã đưa ra lựa chọn của {Male=mình;Female=mình} rồi. Giờ đến lượt ta phải đưa ra lựa chọn của riêng mình.</t>
+          <t>Nhưng {PlayerName} đã đưa ra lựa chọn của {Male=his;Female=her} rồi. Giờ đến lượt ta phải đưa ra lựa chọn của riêng mình.</t>
         </is>
       </c>
     </row>
